--- a/demo_output/figure_00_Amerikansk rentekurve — 2-årig og 10-årig sta.xlsx
+++ b/demo_output/figure_00_Amerikansk rentekurve — 2-årig og 10-årig sta.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-årig amerikansk statsrente" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-årig amerikansk statsrente" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-årig statsrente (USA)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-årig statsrente (USA)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2-årig amerikansk statsrente</t>
+          <t>2-årig statsrente (USA)</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>10-årig amerikansk statsrente</t>
+          <t>10-årig statsrente (USA)</t>
         </is>
       </c>
     </row>
